--- a/CTAS.xlsx
+++ b/CTAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715C2827-E668-4712-A3B8-37B1506654E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC18553-DD24-4C8E-9DF8-4222FB727780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{F251087B-52A6-4D65-A029-73EBA2C6E29C}"/>
   </bookViews>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>SEC</t>
-  </si>
-  <si>
-    <t>CTAS</t>
   </si>
   <si>
     <t>Main</t>
@@ -231,7 +228,10 @@
     <t>Q426</t>
   </si>
   <si>
-    <t>FQ226</t>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>FQ326</t>
   </si>
 </sst>
 </file>
@@ -703,13 +703,13 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K2" s="2">
-        <v>187.97</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -717,7 +717,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="9">
-        <v>401.483</v>
+        <v>400.4</v>
       </c>
       <c r="L3" s="14" t="s">
         <v>64</v>
@@ -732,19 +732,19 @@
       </c>
       <c r="K4" s="3">
         <f>K3*K2</f>
-        <v>75466.759510000004</v>
+        <v>68068</v>
       </c>
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
-        <v>8</v>
+      <c r="B5" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="K5" s="3">
-        <v>200.84200000000001</v>
+        <v>183.20400000000001</v>
       </c>
       <c r="L5" s="14" t="s">
         <v>64</v>
@@ -755,8 +755,8 @@
         <v>5</v>
       </c>
       <c r="K6" s="3">
-        <f>2426.529+550.75</f>
-        <v>2977.279</v>
+        <f>229.49+2427.301</f>
+        <v>2656.7910000000002</v>
       </c>
       <c r="L6" s="14" t="s">
         <v>64</v>
@@ -768,27 +768,28 @@
       </c>
       <c r="K7" s="3">
         <f>K4-K5+K6</f>
-        <v>78243.196509999994</v>
+        <v>70541.587</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{5BCE2AAC-B78B-4D44-8877-F3A1B1EA78E7}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{4088AA47-1B39-45CE-92E1-4DBC4371D5D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -806,95 +807,95 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="K2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="N2" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="Q2" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="R2" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="T2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="W2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="V2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="X2" s="8" t="s">
+      <c r="Z2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="AA2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AC2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AD2" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="AD2" s="8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B3" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="9">
         <v>1697.7719999999999</v>
@@ -941,7 +942,9 @@
       <c r="P3" s="9">
         <v>2155.4</v>
       </c>
-      <c r="Q3" s="9"/>
+      <c r="Q3" s="9">
+        <v>2177.453</v>
+      </c>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
@@ -975,7 +978,7 @@
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="9">
         <v>0</v>
@@ -1019,7 +1022,9 @@
       <c r="P4" s="9">
         <v>0</v>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
@@ -1053,7 +1058,7 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="9">
         <v>468.68200000000002</v>
@@ -1100,7 +1105,9 @@
       <c r="P5" s="9">
         <v>644.59199999999998</v>
       </c>
-      <c r="Q5" s="9"/>
+      <c r="Q5" s="9">
+        <v>663.99099999999999</v>
+      </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
@@ -1134,7 +1141,7 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="10">
         <f>C3+C5</f>
@@ -1191,7 +1198,9 @@
         <f>+P3+P4+P5</f>
         <v>2799.9920000000002</v>
       </c>
-      <c r="Q6" s="10"/>
+      <c r="Q6" s="10">
+        <v>2841.444</v>
+      </c>
       <c r="R6" s="10"/>
       <c r="S6" s="9"/>
       <c r="T6" s="10">
@@ -1239,7 +1248,7 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B7" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="9">
         <v>890.76599999999996</v>
@@ -1286,7 +1295,9 @@
       <c r="P7" s="9">
         <v>1081.2180000000001</v>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="9">
+        <v>1083.019</v>
+      </c>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
@@ -1320,7 +1331,7 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="9">
         <v>247.57599999999999</v>
@@ -1367,7 +1378,9 @@
       <c r="P8" s="9">
         <v>306.28899999999999</v>
       </c>
-      <c r="Q8" s="9"/>
+      <c r="Q8" s="9">
+        <v>309.96899999999999</v>
+      </c>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
       <c r="T8" s="9"/>
@@ -1402,7 +1415,7 @@
     <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9">
         <f t="shared" ref="C9:F9" si="5">C6-SUM(C7:C8)</f>
@@ -1460,7 +1473,10 @@
         <f>P6-SUM(P7:P8)</f>
         <v>1412.4850000000001</v>
       </c>
-      <c r="Q9" s="9"/>
+      <c r="Q9" s="9">
+        <f>Q6-SUM(Q7:Q8)</f>
+        <v>1448.4559999999999</v>
+      </c>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="9">
@@ -1508,7 +1524,7 @@
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="9">
         <v>587.99199999999996</v>
@@ -1555,7 +1571,9 @@
       <c r="P10" s="9">
         <v>756.77099999999996</v>
       </c>
-      <c r="Q10" s="9"/>
+      <c r="Q10" s="9">
+        <v>788.55200000000002</v>
+      </c>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
@@ -1589,14 +1607,14 @@
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="9">
         <f>C9-C10</f>
         <v>440.11999999999989</v>
       </c>
       <c r="D11" s="9">
-        <f t="shared" ref="D11:P11" si="9">D9-D10</f>
+        <f t="shared" ref="D11:Q11" si="9">D9-D10</f>
         <v>444.93400000000008</v>
       </c>
       <c r="E11" s="9">
@@ -1647,7 +1665,10 @@
         <f t="shared" si="9"/>
         <v>655.71400000000017</v>
       </c>
-      <c r="Q11" s="9"/>
+      <c r="Q11" s="9">
+        <f t="shared" si="9"/>
+        <v>659.90399999999988</v>
+      </c>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
       <c r="T11" s="9">
@@ -1695,7 +1716,7 @@
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="9">
         <f>0.155-27.72</f>
@@ -1753,7 +1774,10 @@
         <f>0.866-28.076</f>
         <v>-27.21</v>
       </c>
-      <c r="Q12" s="9"/>
+      <c r="Q12" s="9">
+        <f>-28.212+0.805</f>
+        <v>-27.407</v>
+      </c>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
       <c r="T12" s="9"/>
@@ -1792,7 +1816,7 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B13" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="9">
         <f t="shared" ref="C13:F13" si="12">C11+C12</f>
@@ -1827,30 +1851,33 @@
         <v>527.13900000000035</v>
       </c>
       <c r="K13" s="9">
-        <f>K11+K12</f>
+        <f t="shared" ref="K13:Q13" si="15">K11+K12</f>
         <v>536.66199999999981</v>
       </c>
       <c r="L13" s="9">
-        <f>L11+L12</f>
+        <f t="shared" si="15"/>
         <v>565.68700000000047</v>
       </c>
       <c r="M13" s="9">
-        <f>M11+M12</f>
+        <f t="shared" si="15"/>
         <v>586.4380000000001</v>
       </c>
       <c r="N13" s="9">
-        <f>N11+N12</f>
+        <f t="shared" si="15"/>
         <v>575.41500000000042</v>
       </c>
       <c r="O13" s="9">
-        <f>O11+O12</f>
+        <f t="shared" si="15"/>
         <v>595.9069999999997</v>
       </c>
       <c r="P13" s="9">
-        <f>P11+P12</f>
+        <f t="shared" si="15"/>
         <v>628.50400000000013</v>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="9">
+        <f t="shared" si="15"/>
+        <v>632.49699999999984</v>
+      </c>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
       <c r="T13" s="9">
@@ -1898,7 +1925,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="9">
         <v>60.866</v>
@@ -1945,7 +1972,9 @@
       <c r="P14" s="9">
         <v>133.161</v>
       </c>
-      <c r="Q14" s="9"/>
+      <c r="Q14" s="9">
+        <v>130.001</v>
+      </c>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
       <c r="T14" s="9"/>
@@ -1979,97 +2008,100 @@
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="9">
-        <f t="shared" ref="C15:E15" si="15">C13-C14</f>
+        <f t="shared" ref="C15:E15" si="16">C13-C14</f>
         <v>351.68899999999991</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" ref="D15" si="16">D13-D14</f>
+        <f t="shared" ref="D15" si="17">D13-D14</f>
         <v>324.29300000000006</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>325.82699999999988</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" ref="F15" si="17">F13-F14</f>
+        <f t="shared" ref="F15" si="18">F13-F14</f>
         <v>346.18100000000015</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" ref="G15:AA15" si="18">G13-G14</f>
+        <f t="shared" ref="G15:AA15" si="19">G13-G14</f>
         <v>385.08499999999992</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>374.43299999999977</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" ref="I15" si="19">I13-I14</f>
+        <f t="shared" ref="I15" si="20">I13-I14</f>
         <v>397.5079999999997</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>414.56600000000037</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>452.03299999999979</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>448.49500000000046</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>463.49700000000007</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>448.25600000000043</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>491.1399999999997</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>495.34300000000013</v>
       </c>
-      <c r="Q15" s="9"/>
+      <c r="Q15" s="9">
+        <f t="shared" si="19"/>
+        <v>502.49599999999987</v>
+      </c>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
       <c r="T15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1110.9679999999998</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1235.7569999999992</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1347.9900000000002</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1571.5920000000001</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1812.2810000000006</v>
       </c>
       <c r="AB15" s="9"/>
@@ -2122,7 +2154,7 @@
     </row>
     <row r="17" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="11">
         <v>3.45</v>
@@ -2147,15 +2179,15 @@
         <v>3.9</v>
       </c>
       <c r="J17" s="11">
-        <f t="shared" ref="J17:L17" si="20">+J15/J18</f>
+        <f t="shared" ref="J17:L17" si="21">+J15/J18</f>
         <v>4.0782465839670285</v>
       </c>
       <c r="K17" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.1206077613775522</v>
       </c>
       <c r="L17" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.1112886880204975</v>
       </c>
       <c r="M17" s="11">
@@ -2174,7 +2206,10 @@
         <f>+P15/P18</f>
         <v>1.2337832486057942</v>
       </c>
-      <c r="Q17" s="11"/>
+      <c r="Q17" s="11">
+        <f>+Q15/Q18</f>
+        <v>1.2549850149850148</v>
+      </c>
       <c r="R17" s="11"/>
       <c r="S17" s="9"/>
       <c r="T17" s="9"/>
@@ -2211,26 +2246,26 @@
         <v>2</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:H18" si="21">C15/C17</f>
+        <f t="shared" ref="C18:H18" si="22">C15/C17</f>
         <v>101.93884057971012</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>101.97893081761008</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>102.14012539184949</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>102.11828908554575</v>
       </c>
       <c r="G18" s="9">
         <v>407.58</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>102.02534059945498</v>
       </c>
       <c r="I18" s="9">
@@ -2257,7 +2292,9 @@
       <c r="P18" s="9">
         <v>401.483</v>
       </c>
-      <c r="Q18" s="9"/>
+      <c r="Q18" s="9">
+        <v>400.4</v>
+      </c>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
       <c r="T18" s="9"/>
@@ -2330,7 +2367,7 @@
     </row>
     <row r="20" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2341,63 +2378,66 @@
         <v>7.6013151353656605E-2</v>
       </c>
       <c r="H20" s="12">
-        <f t="shared" ref="H20:P20" si="22">+H3/D3-1</f>
+        <f t="shared" ref="H20:Q20" si="23">+H3/D3-1</f>
         <v>8.2196531318659005E-2</v>
       </c>
       <c r="I20" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9.3509074010948989E-2</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7.7816113863814707E-2</v>
       </c>
       <c r="K20" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.8579228990187859E-2</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7.5582180788115183E-2</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7.7000301602543342E-2</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6.252125638999817E-2</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.1303045393127382E-2</v>
       </c>
       <c r="P20" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.2892469390728474E-2</v>
       </c>
-      <c r="Q20" s="12"/>
+      <c r="Q20" s="12">
+        <f t="shared" si="23"/>
+        <v>7.7336894352901142E-2</v>
+      </c>
       <c r="R20" s="12"/>
       <c r="S20" s="9"/>
       <c r="T20" s="12"/>
       <c r="U20" s="12" t="e">
-        <f t="shared" ref="U20:Y20" si="23">+U3/T3-1</f>
+        <f t="shared" ref="U20:Y20" si="24">+U3/T3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V20" s="12" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W20" s="12" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.4443366460256195E-2</v>
       </c>
       <c r="Y20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.10762038741091207</v>
       </c>
       <c r="Z20" s="12">
@@ -2421,74 +2461,77 @@
     </row>
     <row r="21" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
       <c r="G21" s="12">
-        <f t="shared" ref="G21:J22" si="24">G5/C5-1</f>
+        <f t="shared" ref="G21:J22" si="25">G5/C5-1</f>
         <v>9.9903559343008652E-2</v>
       </c>
       <c r="H21" s="12">
-        <f t="shared" ref="H21" si="25">H5/D5-1</f>
+        <f t="shared" ref="H21" si="26">H5/D5-1</f>
         <v>0.13286266512645439</v>
       </c>
       <c r="I21" s="12">
-        <f t="shared" ref="I21" si="26">I5/E5-1</f>
+        <f t="shared" ref="I21" si="27">I5/E5-1</f>
         <v>0.11757604665052823</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" ref="J21" si="27">J5/F5-1</f>
+        <f t="shared" ref="J21" si="28">J5/F5-1</f>
         <v>9.4823623756760567E-2</v>
       </c>
       <c r="K21" s="12">
-        <f t="shared" ref="K21" si="28">K5/G5-1</f>
+        <f t="shared" ref="K21" si="29">K5/G5-1</f>
         <v>0.10134334293556813</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" ref="L21" si="29">L5/H5-1</f>
+        <f t="shared" ref="L21" si="30">L5/H5-1</f>
         <v>8.4950677414148412E-2</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" ref="M21:M22" si="30">M5/I5-1</f>
+        <f t="shared" ref="M21:M22" si="31">M5/I5-1</f>
         <v>0.11044490313126154</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" ref="N21:P22" si="31">N5/J5-1</f>
+        <f t="shared" ref="N21:Q22" si="32">N5/J5-1</f>
         <v>0.13796818193999028</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.10446183870308645</v>
       </c>
       <c r="P21" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.12814571217050852</v>
       </c>
-      <c r="Q21" s="12"/>
+      <c r="Q21" s="12">
+        <f t="shared" si="32"/>
+        <v>0.12920758824179646</v>
+      </c>
       <c r="R21" s="12"/>
       <c r="S21" s="9"/>
       <c r="T21" s="12"/>
       <c r="U21" s="12" t="e">
-        <f t="shared" ref="U21:Y21" si="32">+(U4+U5)/(+SUM(T4:T5))-1</f>
+        <f t="shared" ref="U21:Y21" si="33">+(U4+U5)/(+SUM(T4:T5))-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V21" s="12" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W21" s="12" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X21" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.14072325941958663</v>
       </c>
       <c r="Y21" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.17890246202869609</v>
       </c>
       <c r="Z21" s="12">
@@ -2512,26 +2555,26 @@
     </row>
     <row r="22" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>8.1181506738661424E-2</v>
       </c>
       <c r="H22" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9.3026303326469773E-2</v>
       </c>
       <c r="I22" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9.8716156176340775E-2</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>8.1622397482830511E-2</v>
       </c>
       <c r="K22" s="13">
@@ -2543,39 +2586,42 @@
         <v>7.7657658643004224E-2</v>
       </c>
       <c r="M22" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.4360517718385264E-2</v>
       </c>
       <c r="N22" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>7.9612373453773699E-2</v>
       </c>
       <c r="O22" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8.6559052313591289E-2</v>
       </c>
       <c r="P22" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9.2985627588285213E-2</v>
       </c>
-      <c r="Q22" s="13"/>
+      <c r="Q22" s="13">
+        <f t="shared" si="32"/>
+        <v>8.902677069507825E-2</v>
+      </c>
       <c r="R22" s="13"/>
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
       <c r="U22" s="13" t="e">
-        <f t="shared" ref="U22:X22" si="33">U6/T6-1</f>
+        <f t="shared" ref="U22:X22" si="34">U6/T6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V22" s="13" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W22" s="13" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X22" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.10372171650033568</v>
       </c>
       <c r="Y22" s="13">
@@ -2583,11 +2629,11 @@
         <v>0.12239035177343238</v>
       </c>
       <c r="Z22" s="13">
-        <f t="shared" ref="Z22:AA22" si="34">Z6/Y6-1</f>
+        <f t="shared" ref="Z22:AA22" si="35">Z6/Y6-1</f>
         <v>8.8573781822096187E-2</v>
       </c>
       <c r="AA22" s="13">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.7482112182264418E-2</v>
       </c>
       <c r="AB22" s="10"/>
@@ -2603,22 +2649,22 @@
     </row>
     <row r="23" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="12">
-        <f t="shared" ref="C23:F23" si="35">(C3-C7)/C3</f>
+        <f t="shared" ref="C23:F23" si="36">(C3-C7)/C3</f>
         <v>0.47533237678557544</v>
       </c>
       <c r="D23" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.46974626122888657</v>
       </c>
       <c r="E23" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.47091742344121917</v>
       </c>
       <c r="F23" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.47739348953251892</v>
       </c>
       <c r="G23" s="12">
@@ -2626,15 +2672,15 @@
         <v>0.48129514321295147</v>
       </c>
       <c r="H23" s="12">
-        <f t="shared" ref="H23:J23" si="36">(H3-H7)/H3</f>
+        <f t="shared" ref="H23:J23" si="37">(H3-H7)/H3</f>
         <v>0.47354288635437614</v>
       </c>
       <c r="I23" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.48833714688257007</v>
       </c>
       <c r="J23" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.48563512785228041</v>
       </c>
       <c r="K23" s="12">
@@ -2646,42 +2692,45 @@
         <v>0.49053109660823652</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" ref="M23:N23" si="37">(M3-M7)/M3</f>
+        <f t="shared" ref="M23:N23" si="38">(M3-M7)/M3</f>
         <v>0.5004512296006618</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.48981966631867169</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" ref="O23:P23" si="38">(O3-O7)/O3</f>
+        <f t="shared" ref="O23:P23" si="39">(O3-O7)/O3</f>
         <v>0.49664286062706764</v>
       </c>
       <c r="P23" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.49836782035817018</v>
       </c>
-      <c r="Q23" s="12"/>
+      <c r="Q23" s="12">
+        <f t="shared" ref="Q23" si="40">(Q3-Q7)/Q3</f>
+        <v>0.50262118172011061</v>
+      </c>
       <c r="R23" s="12"/>
       <c r="S23" s="9"/>
       <c r="T23" s="12" t="e">
-        <f t="shared" ref="T23:X23" si="39">(T3-T7)/T3</f>
+        <f t="shared" ref="T23:X23" si="41">(T3-T7)/T3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U23" s="12" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V23" s="12" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W23" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.47562267647538536</v>
       </c>
       <c r="X23" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.46740908112760915</v>
       </c>
       <c r="Y23" s="12">
@@ -2689,11 +2738,11 @@
         <v>0.47337878218911345</v>
       </c>
       <c r="Z23" s="12">
-        <f t="shared" ref="Z23:AA23" si="40">(Z3-Z7)/Z3</f>
+        <f t="shared" ref="Z23:AA23" si="42">(Z3-Z7)/Z3</f>
         <v>0.48225479320778991</v>
       </c>
       <c r="AA23" s="12">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.49337374419717578</v>
       </c>
       <c r="AB23" s="9"/>
@@ -2709,22 +2758,22 @@
     </row>
     <row r="24" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="12">
-        <f t="shared" ref="C24:F24" si="41">(C5-C8)/C5</f>
+        <f t="shared" ref="C24:F24" si="43">(C5-C8)/C5</f>
         <v>0.47176123683008953</v>
       </c>
       <c r="D24" s="12">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.47150069589197863</v>
       </c>
       <c r="E24" s="12">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.47667579106877916</v>
       </c>
       <c r="F24" s="12">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.473846244119977</v>
       </c>
       <c r="G24" s="12">
@@ -2732,62 +2781,65 @@
         <v>0.50887770244711494</v>
       </c>
       <c r="H24" s="12">
-        <f t="shared" ref="H24:J24" si="42">(H5-H8)/H5</f>
+        <f t="shared" ref="H24:J24" si="44">(H5-H8)/H5</f>
         <v>0.5036448394049009</v>
       </c>
       <c r="I24" s="12">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.51255545001142511</v>
       </c>
       <c r="J24" s="12">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.51328372741158967</v>
       </c>
       <c r="K24" s="12">
-        <f t="shared" ref="K24:L24" si="43">(K5-K8)/K5</f>
+        <f t="shared" ref="K24:L24" si="45">(K5-K8)/K5</f>
         <v>0.52744351367155851</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.52565486993610133</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" ref="M24:N24" si="44">(M5-M8)/M5</f>
+        <f t="shared" ref="M24:N24" si="46">(M5-M8)/M5</f>
         <v>0.52355297058748496</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.52015159222069451</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" ref="O24:P24" si="45">(O5-O8)/O5</f>
+        <f t="shared" ref="O24:P24" si="47">(O5-O8)/O5</f>
         <v>0.52315582659284021</v>
       </c>
       <c r="P24" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.52483276242956789</v>
       </c>
-      <c r="Q24" s="12"/>
+      <c r="Q24" s="12">
+        <f t="shared" ref="Q24" si="48">(Q5-Q8)/Q5</f>
+        <v>0.53317288939157303</v>
+      </c>
       <c r="R24" s="12"/>
       <c r="S24" s="9"/>
       <c r="T24" s="12" t="e">
-        <f t="shared" ref="T24:X24" si="46">(T4+T5-T8)/(T4+T5)</f>
+        <f t="shared" ref="T24:X24" si="49">(T4+T5-T8)/(T4+T5)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U24" s="12" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V24" s="12" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W24" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>0.42652946503419065</v>
       </c>
       <c r="X24" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>0.44344596765918326</v>
       </c>
       <c r="Y24" s="12">
@@ -2795,11 +2847,11 @@
         <v>0.47346739016563305</v>
       </c>
       <c r="Z24" s="12">
-        <f t="shared" ref="Z24:AA24" si="47">(Z4+Z5-Z8)/(Z4+Z5)</f>
+        <f t="shared" ref="Z24:AA24" si="50">(Z4+Z5-Z8)/(Z4+Z5)</f>
         <v>0.50965555292819431</v>
       </c>
       <c r="AA24" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.52407884918963099</v>
       </c>
       <c r="AB24" s="9"/>
@@ -2815,22 +2867,22 @@
     </row>
     <row r="25" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" s="12">
-        <f t="shared" ref="C25:F25" si="48">C9/C6</f>
+        <f t="shared" ref="C25:F25" si="51">C9/C6</f>
         <v>0.47455981063987512</v>
       </c>
       <c r="D25" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.47012126768736168</v>
       </c>
       <c r="E25" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.47216329236807908</v>
       </c>
       <c r="F25" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.47659961540330342</v>
       </c>
       <c r="G25" s="12">
@@ -2838,62 +2890,65 @@
         <v>0.48736557188782109</v>
       </c>
       <c r="H25" s="12">
-        <f t="shared" ref="H25:J25" si="49">H9/H6</f>
+        <f t="shared" ref="H25:J25" si="52">H9/H6</f>
         <v>0.4802116123452313</v>
       </c>
       <c r="I25" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.49366691422437198</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.49189841092541897</v>
       </c>
       <c r="K25" s="12">
-        <f t="shared" ref="K25:L25" si="50">K9/K6</f>
+        <f t="shared" ref="K25:L25" si="53">K9/K6</f>
         <v>0.50053466059745266</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0.49836500593531935</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" ref="M25:N25" si="51">M9/M6</f>
+        <f t="shared" ref="M25:N25" si="54">M9/M6</f>
         <v>0.50565757012125367</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0.49706221051321553</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" ref="O25:P25" si="52">O9/O6</f>
+        <f t="shared" ref="O25:P25" si="55">O9/O6</f>
         <v>0.5027592580465482</v>
       </c>
       <c r="P25" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>0.50446036988677112</v>
       </c>
-      <c r="Q25" s="12"/>
+      <c r="Q25" s="12">
+        <f t="shared" ref="Q25" si="56">Q9/Q6</f>
+        <v>0.50976053020928791</v>
+      </c>
       <c r="R25" s="12"/>
       <c r="S25" s="9"/>
       <c r="T25" s="12" t="e">
-        <f t="shared" ref="T25:X25" si="53">T9/T6</f>
+        <f t="shared" ref="T25:X25" si="57">T9/T6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U25" s="12" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V25" s="12" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W25" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>0.46578030279610022</v>
       </c>
       <c r="X25" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>0.46244381694525361</v>
       </c>
       <c r="Y25" s="12">
@@ -2901,11 +2956,11 @@
         <v>0.47339806657819644</v>
       </c>
       <c r="Z25" s="12">
-        <f t="shared" ref="Z25:AA25" si="54">Z9/Z6</f>
+        <f t="shared" ref="Z25:AA25" si="58">Z9/Z6</f>
         <v>0.48834052423693147</v>
       </c>
       <c r="AA25" s="12">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>0.50039394861656683</v>
       </c>
       <c r="AB25" s="9"/>
@@ -2921,22 +2976,22 @@
     </row>
     <row r="26" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="12">
-        <f t="shared" ref="C26:F26" si="55">C11/C6</f>
+        <f t="shared" ref="C26:F26" si="59">C11/C6</f>
         <v>0.20315224786679059</v>
       </c>
       <c r="D26" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.2045807128557359</v>
       </c>
       <c r="E26" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.20402504856195425</v>
       </c>
       <c r="F26" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>0.20608622302493668</v>
       </c>
       <c r="G26" s="12">
@@ -2944,62 +2999,65 @@
         <v>0.21370003372710078</v>
       </c>
       <c r="H26" s="12">
-        <f t="shared" ref="H26:J26" si="56">H11/H6</f>
+        <f t="shared" ref="H26:J26" si="60">H11/H6</f>
         <v>0.21020016599521191</v>
       </c>
       <c r="I26" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>0.21644328982163782</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>0.22161408535635307</v>
       </c>
       <c r="K26" s="12">
-        <f t="shared" ref="K26:L26" si="57">K11/K6</f>
+        <f t="shared" ref="K26:L26" si="61">K11/K6</f>
         <v>0.22427003338280851</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v>0.23085093468104065</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" ref="M26:N26" si="58">M11/M6</f>
+        <f t="shared" ref="M26:N26" si="62">M11/M6</f>
         <v>0.23373546801862211</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>0.22396174613480332</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" ref="O26:P26" si="59">O11/O6</f>
+        <f t="shared" ref="O26:P26" si="63">O11/O6</f>
         <v>0.22731098898430599</v>
       </c>
       <c r="P26" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.23418424052640155</v>
       </c>
-      <c r="Q26" s="12"/>
+      <c r="Q26" s="12">
+        <f t="shared" ref="Q26" si="64">Q11/Q6</f>
+        <v>0.23224247952801458</v>
+      </c>
       <c r="R26" s="12"/>
       <c r="S26" s="9"/>
       <c r="T26" s="12" t="e">
-        <f t="shared" ref="T26:X26" si="60">T11/T6</f>
+        <f t="shared" ref="T26:X26" si="65">T11/T6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U26" s="12" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V26" s="12" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W26" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0.19469165329368746</v>
       </c>
       <c r="X26" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>0.20209794207341325</v>
       </c>
       <c r="Y26" s="12">
@@ -3007,11 +3065,11 @@
         <v>0.20448176443824698</v>
       </c>
       <c r="Z26" s="12">
-        <f t="shared" ref="Z26:AA26" si="61">Z11/Z6</f>
+        <f t="shared" ref="Z26:AA26" si="66">Z11/Z6</f>
         <v>0.21555861103107712</v>
       </c>
       <c r="AA26" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>0.22820935146106247</v>
       </c>
       <c r="AB26" s="9"/>
@@ -3027,22 +3085,22 @@
     </row>
     <row r="27" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="12">
-        <f t="shared" ref="C27:F27" si="62">C15/C6</f>
+        <f t="shared" ref="C27:F27" si="67">C15/C6</f>
         <v>0.16233393369995391</v>
       </c>
       <c r="D27" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0.14910996488046577</v>
       </c>
       <c r="E27" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0.1487804031623946</v>
       </c>
       <c r="F27" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>0.15153661394694881</v>
       </c>
       <c r="G27" s="12">
@@ -3050,62 +3108,65 @@
         <v>0.16440253935184193</v>
       </c>
       <c r="H27" s="12">
-        <f t="shared" ref="H27:J27" si="63">H15/H6</f>
+        <f t="shared" ref="H27:J27" si="68">H15/H6</f>
         <v>0.15751161987517118</v>
       </c>
       <c r="I27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0.1652034163794539</v>
       </c>
       <c r="J27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>0.16777697511265993</v>
       </c>
       <c r="K27" s="12">
-        <f t="shared" ref="K27:L27" si="64">K15/K6</f>
+        <f t="shared" ref="K27:L27" si="69">K15/K6</f>
         <v>0.18069849259689941</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>0.17507142486307403</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" ref="M27:N27" si="65">M15/M6</f>
+        <f t="shared" ref="M27:N27" si="70">M15/M6</f>
         <v>0.1776422977672116</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>0.16803391146971208</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" ref="O27:P27" si="66">O15/O6</f>
+        <f t="shared" ref="O27:P27" si="71">O15/O6</f>
         <v>0.18069093293089852</v>
       </c>
       <c r="P27" s="12">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>0.17690871973919928</v>
       </c>
-      <c r="Q27" s="12"/>
+      <c r="Q27" s="12">
+        <f t="shared" ref="Q27" si="72">Q15/Q6</f>
+        <v>0.17684529415325442</v>
+      </c>
       <c r="R27" s="12"/>
       <c r="S27" s="9"/>
       <c r="T27" s="12" t="e">
-        <f t="shared" ref="T27:X27" si="67">T15/T6</f>
+        <f t="shared" ref="T27:X27" si="73">T15/T6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U27" s="12" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V27" s="12" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W27" s="12">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>0.15611508162903961</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>0.15733190535465261</v>
       </c>
       <c r="Y27" s="12">
@@ -3113,11 +3174,11 @@
         <v>0.15290668346686492</v>
       </c>
       <c r="Z27" s="12">
-        <f t="shared" ref="Z27:AA27" si="68">Z15/Z6</f>
+        <f t="shared" ref="Z27:AA27" si="74">Z15/Z6</f>
         <v>0.16376524430749803</v>
       </c>
       <c r="AA27" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>0.17526588751202715</v>
       </c>
       <c r="AB27" s="9"/>
@@ -3133,22 +3194,22 @@
     </row>
     <row r="28" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" s="12">
-        <f t="shared" ref="C28:F28" si="69">C14/C13</f>
+        <f t="shared" ref="C28:F28" si="75">C14/C13</f>
         <v>0.14753426815818502</v>
       </c>
       <c r="D28" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>0.22111980555195285</v>
       </c>
       <c r="E28" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>0.22119149261651289</v>
       </c>
       <c r="F28" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>0.22358136582718244</v>
       </c>
       <c r="G28" s="12">
@@ -3156,62 +3217,65 @@
         <v>0.19173484679934685</v>
       </c>
       <c r="H28" s="12">
-        <f t="shared" ref="H28:J28" si="70">H14/H13</f>
+        <f t="shared" ref="H28:J28" si="76">H14/H13</f>
         <v>0.20982691163250072</v>
       </c>
       <c r="I28" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>0.19889560661023792</v>
       </c>
       <c r="J28" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>0.21355467912637824</v>
       </c>
       <c r="K28" s="12">
-        <f t="shared" ref="K28:L28" si="71">K14/K13</f>
+        <f t="shared" ref="K28:L28" si="77">K14/K13</f>
         <v>0.15769516008213744</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="77"/>
         <v>0.20716756793067526</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" ref="M28:N28" si="72">M14/M13</f>
+        <f t="shared" ref="M28:N28" si="78">M14/M13</f>
         <v>0.20964023477332638</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="72"/>
+        <f t="shared" si="78"/>
         <v>0.22098659228556763</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" ref="O28:P28" si="73">O14/O13</f>
+        <f t="shared" ref="O28:P28" si="79">O14/O13</f>
         <v>0.17581099064115718</v>
       </c>
       <c r="P28" s="12">
-        <f t="shared" si="73"/>
+        <f t="shared" si="79"/>
         <v>0.21186977330295428</v>
       </c>
-      <c r="Q28" s="12"/>
+      <c r="Q28" s="12">
+        <f t="shared" ref="Q28" si="80">Q14/Q13</f>
+        <v>0.20553615274064546</v>
+      </c>
       <c r="R28" s="12"/>
       <c r="S28" s="9"/>
       <c r="T28" s="12" t="e">
-        <f t="shared" ref="T28:X28" si="74">T14/T13</f>
+        <f t="shared" ref="T28:X28" si="81">T14/T13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U28" s="12" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V28" s="12" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W28" s="12">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0.13727908156014879</v>
       </c>
       <c r="X28" s="12">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0.17548479818090604</v>
       </c>
       <c r="Y28" s="12">
@@ -3219,11 +3283,11 @@
         <v>0.20385577634087509</v>
       </c>
       <c r="Z28" s="12">
-        <f t="shared" ref="Z28:AA28" si="75">Z14/Z13</f>
+        <f t="shared" ref="Z28:AA28" si="82">Z14/Z13</f>
         <v>0.20370686575785288</v>
       </c>
       <c r="AA28" s="12">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0.19959394082330104</v>
       </c>
       <c r="AB28" s="9"/>

--- a/CTAS.xlsx
+++ b/CTAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC18553-DD24-4C8E-9DF8-4222FB727780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3009995A-A1CF-44FA-AD6C-67B91992D3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{F251087B-52A6-4D65-A029-73EBA2C6E29C}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{F251087B-52A6-4D65-A029-73EBA2C6E29C}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2">
-        <v>170</v>
+        <v>202.53</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -732,7 +732,7 @@
       </c>
       <c r="K4" s="3">
         <f>K3*K2</f>
-        <v>68068</v>
+        <v>81093.012000000002</v>
       </c>
       <c r="L4" s="4"/>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="K7" s="3">
         <f>K4-K5+K6</f>
-        <v>70541.587</v>
+        <v>83566.599000000002</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1454,49 +1454,49 @@
         <v>1252.1309999999999</v>
       </c>
       <c r="L9" s="9">
-        <f>L6-SUM(L7:L8)</f>
+        <f t="shared" ref="L9:Q9" si="8">L6-SUM(L7:L8)</f>
         <v>1276.7030000000004</v>
       </c>
       <c r="M9" s="9">
-        <f>M6-SUM(M7:M8)</f>
+        <f t="shared" si="8"/>
         <v>1319.3410000000001</v>
       </c>
       <c r="N9" s="9">
-        <f>N6-SUM(N7:N8)</f>
+        <f t="shared" si="8"/>
         <v>1325.9890000000007</v>
       </c>
       <c r="O9" s="9">
-        <f>O6-SUM(O7:O8)</f>
+        <f t="shared" si="8"/>
         <v>1366.5609999999997</v>
       </c>
       <c r="P9" s="9">
-        <f>P6-SUM(P7:P8)</f>
+        <f t="shared" si="8"/>
         <v>1412.4850000000001</v>
       </c>
       <c r="Q9" s="9">
-        <f>Q6-SUM(Q7:Q8)</f>
+        <f t="shared" si="8"/>
         <v>1448.4559999999999</v>
       </c>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="9">
-        <f t="shared" ref="T9:X9" si="8">T6-SUM(T7:T8)</f>
+        <f t="shared" ref="T9:X9" si="9">T6-SUM(T7:T8)</f>
         <v>0</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3314.6509999999998</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3632.2459999999992</v>
       </c>
       <c r="Y9" s="9">
@@ -1614,7 +1614,7 @@
         <v>440.11999999999989</v>
       </c>
       <c r="D11" s="9">
-        <f t="shared" ref="D11:Q11" si="9">D9-D10</f>
+        <f t="shared" ref="D11:Q11" si="10">D9-D10</f>
         <v>444.93400000000008</v>
       </c>
       <c r="E11" s="9">
@@ -1622,73 +1622,73 @@
         <v>446.8119999999999</v>
       </c>
       <c r="F11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>470.79800000000023</v>
       </c>
       <c r="G11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>500.55599999999993</v>
       </c>
       <c r="H11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>499.68299999999977</v>
       </c>
       <c r="I11" s="9">
-        <f t="shared" ref="I11" si="10">I9-I10</f>
+        <f t="shared" ref="I11" si="11">I9-I10</f>
         <v>520.79999999999973</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>547.59400000000028</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>561.03099999999984</v>
       </c>
       <c r="L11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>591.39000000000044</v>
       </c>
       <c r="M11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>609.85300000000007</v>
       </c>
       <c r="N11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>597.45200000000045</v>
       </c>
       <c r="O11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>617.8589999999997</v>
       </c>
       <c r="P11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>655.71400000000017</v>
       </c>
       <c r="Q11" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>659.90399999999988</v>
       </c>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
       <c r="T11" s="9">
-        <f t="shared" ref="T11:X11" si="11">T9-T10</f>
+        <f t="shared" ref="T11:X11" si="12">T9-T10</f>
         <v>0</v>
       </c>
       <c r="U11" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="V11" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="W11" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1385.4919999999997</v>
       </c>
       <c r="X11" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1587.3699999999992</v>
       </c>
       <c r="Y11" s="9">
@@ -1819,19 +1819,19 @@
         <v>24</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" ref="C13:F13" si="12">C11+C12</f>
+        <f t="shared" ref="C13:F13" si="13">C11+C12</f>
         <v>412.55499999999989</v>
       </c>
       <c r="D13" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>416.35800000000006</v>
       </c>
       <c r="E13" s="9">
-        <f t="shared" ref="E13" si="13">E11+E12</f>
+        <f t="shared" ref="E13" si="14">E11+E12</f>
         <v>418.36599999999987</v>
       </c>
       <c r="F13" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>445.8690000000002</v>
       </c>
       <c r="G13" s="9">
@@ -1839,7 +1839,7 @@
         <v>476.43399999999991</v>
       </c>
       <c r="H13" s="9">
-        <f t="shared" ref="H13:AA13" si="14">H11+H12</f>
+        <f t="shared" ref="H13:AA13" si="15">H11+H12</f>
         <v>473.86199999999974</v>
       </c>
       <c r="I13" s="9">
@@ -1847,69 +1847,69 @@
         <v>496.1999999999997</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>527.13900000000035</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" ref="K13:Q13" si="15">K11+K12</f>
+        <f t="shared" ref="K13:Q13" si="16">K11+K12</f>
         <v>536.66199999999981</v>
       </c>
       <c r="L13" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>565.68700000000047</v>
       </c>
       <c r="M13" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>586.4380000000001</v>
       </c>
       <c r="N13" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>575.41500000000042</v>
       </c>
       <c r="O13" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>595.9069999999997</v>
       </c>
       <c r="P13" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>628.50400000000013</v>
       </c>
       <c r="Q13" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>632.49699999999984</v>
       </c>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
       <c r="T13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="W13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1287.7489999999998</v>
       </c>
       <c r="X13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1498.7679999999991</v>
       </c>
       <c r="Y13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1693.1480000000001</v>
       </c>
       <c r="Z13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1973.6350000000002</v>
       </c>
       <c r="AA13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2264.2020000000007</v>
       </c>
       <c r="AB13" s="9"/>
@@ -2011,97 +2011,97 @@
         <v>26</v>
       </c>
       <c r="C15" s="9">
-        <f t="shared" ref="C15:E15" si="16">C13-C14</f>
+        <f t="shared" ref="C15:E15" si="17">C13-C14</f>
         <v>351.68899999999991</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" ref="D15" si="17">D13-D14</f>
+        <f t="shared" ref="D15" si="18">D13-D14</f>
         <v>324.29300000000006</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>325.82699999999988</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" ref="F15" si="18">F13-F14</f>
+        <f t="shared" ref="F15" si="19">F13-F14</f>
         <v>346.18100000000015</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" ref="G15:AA15" si="19">G13-G14</f>
+        <f t="shared" ref="G15:AA15" si="20">G13-G14</f>
         <v>385.08499999999992</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>374.43299999999977</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" ref="I15" si="20">I13-I14</f>
+        <f t="shared" ref="I15" si="21">I13-I14</f>
         <v>397.5079999999997</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>414.56600000000037</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>452.03299999999979</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>448.49500000000046</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>463.49700000000007</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>448.25600000000043</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>491.1399999999997</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>495.34300000000013</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>502.49599999999987</v>
       </c>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
       <c r="T15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1110.9679999999998</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1235.7569999999992</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1347.9900000000002</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1571.5920000000001</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1812.2810000000006</v>
       </c>
       <c r="AB15" s="9"/>
@@ -2179,15 +2179,15 @@
         <v>3.9</v>
       </c>
       <c r="J17" s="11">
-        <f t="shared" ref="J17:L17" si="21">+J15/J18</f>
+        <f t="shared" ref="J17:L17" si="22">+J15/J18</f>
         <v>4.0782465839670285</v>
       </c>
       <c r="K17" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.1206077613775522</v>
       </c>
       <c r="L17" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.1112886880204975</v>
       </c>
       <c r="M17" s="11">
@@ -2246,26 +2246,26 @@
         <v>2</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:H18" si="22">C15/C17</f>
+        <f t="shared" ref="C18:H18" si="23">C15/C17</f>
         <v>101.93884057971012</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>101.97893081761008</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>102.14012539184949</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>102.11828908554575</v>
       </c>
       <c r="G18" s="9">
         <v>407.58</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>102.02534059945498</v>
       </c>
       <c r="I18" s="9">
@@ -2378,66 +2378,66 @@
         <v>7.6013151353656605E-2</v>
       </c>
       <c r="H20" s="12">
-        <f t="shared" ref="H20:Q20" si="23">+H3/D3-1</f>
+        <f t="shared" ref="H20:Q20" si="24">+H3/D3-1</f>
         <v>8.2196531318659005E-2</v>
       </c>
       <c r="I20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.3509074010948989E-2</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.7816113863814707E-2</v>
       </c>
       <c r="K20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.8579228990187859E-2</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.5582180788115183E-2</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.7000301602543342E-2</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.252125638999817E-2</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.1303045393127382E-2</v>
       </c>
       <c r="P20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.2892469390728474E-2</v>
       </c>
       <c r="Q20" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.7336894352901142E-2</v>
       </c>
       <c r="R20" s="12"/>
       <c r="S20" s="9"/>
       <c r="T20" s="12"/>
       <c r="U20" s="12" t="e">
-        <f t="shared" ref="U20:Y20" si="24">+U3/T3-1</f>
+        <f t="shared" ref="U20:Y20" si="25">+U3/T3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V20" s="12" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W20" s="12" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X20" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9.4443366460256195E-2</v>
       </c>
       <c r="Y20" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.10762038741091207</v>
       </c>
       <c r="Z20" s="12">
@@ -2468,70 +2468,70 @@
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
       <c r="G21" s="12">
-        <f t="shared" ref="G21:J22" si="25">G5/C5-1</f>
+        <f t="shared" ref="G21:J22" si="26">G5/C5-1</f>
         <v>9.9903559343008652E-2</v>
       </c>
       <c r="H21" s="12">
-        <f t="shared" ref="H21" si="26">H5/D5-1</f>
+        <f t="shared" ref="H21" si="27">H5/D5-1</f>
         <v>0.13286266512645439</v>
       </c>
       <c r="I21" s="12">
-        <f t="shared" ref="I21" si="27">I5/E5-1</f>
+        <f t="shared" ref="I21" si="28">I5/E5-1</f>
         <v>0.11757604665052823</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" ref="J21" si="28">J5/F5-1</f>
+        <f t="shared" ref="J21" si="29">J5/F5-1</f>
         <v>9.4823623756760567E-2</v>
       </c>
       <c r="K21" s="12">
-        <f t="shared" ref="K21" si="29">K5/G5-1</f>
+        <f t="shared" ref="K21" si="30">K5/G5-1</f>
         <v>0.10134334293556813</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" ref="L21" si="30">L5/H5-1</f>
+        <f t="shared" ref="L21" si="31">L5/H5-1</f>
         <v>8.4950677414148412E-2</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" ref="M21:M22" si="31">M5/I5-1</f>
+        <f t="shared" ref="M21:M22" si="32">M5/I5-1</f>
         <v>0.11044490313126154</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" ref="N21:Q22" si="32">N5/J5-1</f>
+        <f t="shared" ref="N21:Q22" si="33">N5/J5-1</f>
         <v>0.13796818193999028</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.10446183870308645</v>
       </c>
       <c r="P21" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.12814571217050852</v>
       </c>
       <c r="Q21" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.12920758824179646</v>
       </c>
       <c r="R21" s="12"/>
       <c r="S21" s="9"/>
       <c r="T21" s="12"/>
       <c r="U21" s="12" t="e">
-        <f t="shared" ref="U21:Y21" si="33">+(U4+U5)/(+SUM(T4:T5))-1</f>
+        <f t="shared" ref="U21:Y21" si="34">+(U4+U5)/(+SUM(T4:T5))-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V21" s="12" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W21" s="12" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X21" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.14072325941958663</v>
       </c>
       <c r="Y21" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.17890246202869609</v>
       </c>
       <c r="Z21" s="12">
@@ -2562,19 +2562,19 @@
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.1181506738661424E-2</v>
       </c>
       <c r="H22" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9.3026303326469773E-2</v>
       </c>
       <c r="I22" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9.8716156176340775E-2</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.1622397482830511E-2</v>
       </c>
       <c r="K22" s="13">
@@ -2586,42 +2586,42 @@
         <v>7.7657658643004224E-2</v>
       </c>
       <c r="M22" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8.4360517718385264E-2</v>
       </c>
       <c r="N22" s="13">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.9612373453773699E-2</v>
       </c>
       <c r="O22" s="13">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.6559052313591289E-2</v>
       </c>
       <c r="P22" s="13">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>9.2985627588285213E-2</v>
       </c>
       <c r="Q22" s="13">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.902677069507825E-2</v>
       </c>
       <c r="R22" s="13"/>
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
       <c r="U22" s="13" t="e">
-        <f t="shared" ref="U22:X22" si="34">U6/T6-1</f>
+        <f t="shared" ref="U22:X22" si="35">U6/T6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V22" s="13" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W22" s="13" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X22" s="13">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.10372171650033568</v>
       </c>
       <c r="Y22" s="13">
@@ -2629,11 +2629,11 @@
         <v>0.12239035177343238</v>
       </c>
       <c r="Z22" s="13">
-        <f t="shared" ref="Z22:AA22" si="35">Z6/Y6-1</f>
+        <f t="shared" ref="Z22:AA22" si="36">Z6/Y6-1</f>
         <v>8.8573781822096187E-2</v>
       </c>
       <c r="AA22" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7.7482112182264418E-2</v>
       </c>
       <c r="AB22" s="10"/>
@@ -2652,19 +2652,19 @@
         <v>33</v>
       </c>
       <c r="C23" s="12">
-        <f t="shared" ref="C23:F23" si="36">(C3-C7)/C3</f>
+        <f t="shared" ref="C23:F23" si="37">(C3-C7)/C3</f>
         <v>0.47533237678557544</v>
       </c>
       <c r="D23" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.46974626122888657</v>
       </c>
       <c r="E23" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.47091742344121917</v>
       </c>
       <c r="F23" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.47739348953251892</v>
       </c>
       <c r="G23" s="12">
@@ -2672,15 +2672,15 @@
         <v>0.48129514321295147</v>
       </c>
       <c r="H23" s="12">
-        <f t="shared" ref="H23:J23" si="37">(H3-H7)/H3</f>
+        <f t="shared" ref="H23:J23" si="38">(H3-H7)/H3</f>
         <v>0.47354288635437614</v>
       </c>
       <c r="I23" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.48833714688257007</v>
       </c>
       <c r="J23" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.48563512785228041</v>
       </c>
       <c r="K23" s="12">
@@ -2692,45 +2692,45 @@
         <v>0.49053109660823652</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" ref="M23:N23" si="38">(M3-M7)/M3</f>
+        <f t="shared" ref="M23:N23" si="39">(M3-M7)/M3</f>
         <v>0.5004512296006618</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.48981966631867169</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" ref="O23:P23" si="39">(O3-O7)/O3</f>
+        <f t="shared" ref="O23:P23" si="40">(O3-O7)/O3</f>
         <v>0.49664286062706764</v>
       </c>
       <c r="P23" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.49836782035817018</v>
       </c>
       <c r="Q23" s="12">
-        <f t="shared" ref="Q23" si="40">(Q3-Q7)/Q3</f>
+        <f t="shared" ref="Q23" si="41">(Q3-Q7)/Q3</f>
         <v>0.50262118172011061</v>
       </c>
       <c r="R23" s="12"/>
       <c r="S23" s="9"/>
       <c r="T23" s="12" t="e">
-        <f t="shared" ref="T23:X23" si="41">(T3-T7)/T3</f>
+        <f t="shared" ref="T23:X23" si="42">(T3-T7)/T3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U23" s="12" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V23" s="12" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W23" s="12">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.47562267647538536</v>
       </c>
       <c r="X23" s="12">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.46740908112760915</v>
       </c>
       <c r="Y23" s="12">
@@ -2738,11 +2738,11 @@
         <v>0.47337878218911345</v>
       </c>
       <c r="Z23" s="12">
-        <f t="shared" ref="Z23:AA23" si="42">(Z3-Z7)/Z3</f>
+        <f t="shared" ref="Z23:AA23" si="43">(Z3-Z7)/Z3</f>
         <v>0.48225479320778991</v>
       </c>
       <c r="AA23" s="12">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.49337374419717578</v>
       </c>
       <c r="AB23" s="9"/>
@@ -2761,19 +2761,19 @@
         <v>34</v>
       </c>
       <c r="C24" s="12">
-        <f t="shared" ref="C24:F24" si="43">(C5-C8)/C5</f>
+        <f t="shared" ref="C24:F24" si="44">(C5-C8)/C5</f>
         <v>0.47176123683008953</v>
       </c>
       <c r="D24" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.47150069589197863</v>
       </c>
       <c r="E24" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.47667579106877916</v>
       </c>
       <c r="F24" s="12">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.473846244119977</v>
       </c>
       <c r="G24" s="12">
@@ -2781,65 +2781,65 @@
         <v>0.50887770244711494</v>
       </c>
       <c r="H24" s="12">
-        <f t="shared" ref="H24:J24" si="44">(H5-H8)/H5</f>
+        <f t="shared" ref="H24:J24" si="45">(H5-H8)/H5</f>
         <v>0.5036448394049009</v>
       </c>
       <c r="I24" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.51255545001142511</v>
       </c>
       <c r="J24" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.51328372741158967</v>
       </c>
       <c r="K24" s="12">
-        <f t="shared" ref="K24:L24" si="45">(K5-K8)/K5</f>
+        <f t="shared" ref="K24:L24" si="46">(K5-K8)/K5</f>
         <v>0.52744351367155851</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.52565486993610133</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" ref="M24:N24" si="46">(M5-M8)/M5</f>
+        <f t="shared" ref="M24:N24" si="47">(M5-M8)/M5</f>
         <v>0.52355297058748496</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.52015159222069451</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" ref="O24:P24" si="47">(O5-O8)/O5</f>
+        <f t="shared" ref="O24:P24" si="48">(O5-O8)/O5</f>
         <v>0.52315582659284021</v>
       </c>
       <c r="P24" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.52483276242956789</v>
       </c>
       <c r="Q24" s="12">
-        <f t="shared" ref="Q24" si="48">(Q5-Q8)/Q5</f>
+        <f t="shared" ref="Q24" si="49">(Q5-Q8)/Q5</f>
         <v>0.53317288939157303</v>
       </c>
       <c r="R24" s="12"/>
       <c r="S24" s="9"/>
       <c r="T24" s="12" t="e">
-        <f t="shared" ref="T24:X24" si="49">(T4+T5-T8)/(T4+T5)</f>
+        <f t="shared" ref="T24:X24" si="50">(T4+T5-T8)/(T4+T5)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U24" s="12" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V24" s="12" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W24" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.42652946503419065</v>
       </c>
       <c r="X24" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.44344596765918326</v>
       </c>
       <c r="Y24" s="12">
@@ -2847,11 +2847,11 @@
         <v>0.47346739016563305</v>
       </c>
       <c r="Z24" s="12">
-        <f t="shared" ref="Z24:AA24" si="50">(Z4+Z5-Z8)/(Z4+Z5)</f>
+        <f t="shared" ref="Z24:AA24" si="51">(Z4+Z5-Z8)/(Z4+Z5)</f>
         <v>0.50965555292819431</v>
       </c>
       <c r="AA24" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.52407884918963099</v>
       </c>
       <c r="AB24" s="9"/>
@@ -2870,19 +2870,19 @@
         <v>30</v>
       </c>
       <c r="C25" s="12">
-        <f t="shared" ref="C25:F25" si="51">C9/C6</f>
+        <f t="shared" ref="C25:F25" si="52">C9/C6</f>
         <v>0.47455981063987512</v>
       </c>
       <c r="D25" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.47012126768736168</v>
       </c>
       <c r="E25" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.47216329236807908</v>
       </c>
       <c r="F25" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.47659961540330342</v>
       </c>
       <c r="G25" s="12">
@@ -2890,65 +2890,65 @@
         <v>0.48736557188782109</v>
       </c>
       <c r="H25" s="12">
-        <f t="shared" ref="H25:J25" si="52">H9/H6</f>
+        <f t="shared" ref="H25:J25" si="53">H9/H6</f>
         <v>0.4802116123452313</v>
       </c>
       <c r="I25" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.49366691422437198</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.49189841092541897</v>
       </c>
       <c r="K25" s="12">
-        <f t="shared" ref="K25:L25" si="53">K9/K6</f>
+        <f t="shared" ref="K25:L25" si="54">K9/K6</f>
         <v>0.50053466059745266</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.49836500593531935</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" ref="M25:N25" si="54">M9/M6</f>
+        <f t="shared" ref="M25:N25" si="55">M9/M6</f>
         <v>0.50565757012125367</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.49706221051321553</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" ref="O25:P25" si="55">O9/O6</f>
+        <f t="shared" ref="O25:P25" si="56">O9/O6</f>
         <v>0.5027592580465482</v>
       </c>
       <c r="P25" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.50446036988677112</v>
       </c>
       <c r="Q25" s="12">
-        <f t="shared" ref="Q25" si="56">Q9/Q6</f>
+        <f t="shared" ref="Q25" si="57">Q9/Q6</f>
         <v>0.50976053020928791</v>
       </c>
       <c r="R25" s="12"/>
       <c r="S25" s="9"/>
       <c r="T25" s="12" t="e">
-        <f t="shared" ref="T25:X25" si="57">T9/T6</f>
+        <f t="shared" ref="T25:X25" si="58">T9/T6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U25" s="12" t="e">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V25" s="12" t="e">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W25" s="12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.46578030279610022</v>
       </c>
       <c r="X25" s="12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.46244381694525361</v>
       </c>
       <c r="Y25" s="12">
@@ -2956,11 +2956,11 @@
         <v>0.47339806657819644</v>
       </c>
       <c r="Z25" s="12">
-        <f t="shared" ref="Z25:AA25" si="58">Z9/Z6</f>
+        <f t="shared" ref="Z25:AA25" si="59">Z9/Z6</f>
         <v>0.48834052423693147</v>
       </c>
       <c r="AA25" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.50039394861656683</v>
       </c>
       <c r="AB25" s="9"/>
@@ -2979,19 +2979,19 @@
         <v>31</v>
       </c>
       <c r="C26" s="12">
-        <f t="shared" ref="C26:F26" si="59">C11/C6</f>
+        <f t="shared" ref="C26:F26" si="60">C11/C6</f>
         <v>0.20315224786679059</v>
       </c>
       <c r="D26" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.2045807128557359</v>
       </c>
       <c r="E26" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.20402504856195425</v>
       </c>
       <c r="F26" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.20608622302493668</v>
       </c>
       <c r="G26" s="12">
@@ -2999,65 +2999,65 @@
         <v>0.21370003372710078</v>
       </c>
       <c r="H26" s="12">
-        <f t="shared" ref="H26:J26" si="60">H11/H6</f>
+        <f t="shared" ref="H26:J26" si="61">H11/H6</f>
         <v>0.21020016599521191</v>
       </c>
       <c r="I26" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.21644328982163782</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.22161408535635307</v>
       </c>
       <c r="K26" s="12">
-        <f t="shared" ref="K26:L26" si="61">K11/K6</f>
+        <f t="shared" ref="K26:L26" si="62">K11/K6</f>
         <v>0.22427003338280851</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.23085093468104065</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" ref="M26:N26" si="62">M11/M6</f>
+        <f t="shared" ref="M26:N26" si="63">M11/M6</f>
         <v>0.23373546801862211</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.22396174613480332</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" ref="O26:P26" si="63">O11/O6</f>
+        <f t="shared" ref="O26:P26" si="64">O11/O6</f>
         <v>0.22731098898430599</v>
       </c>
       <c r="P26" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.23418424052640155</v>
       </c>
       <c r="Q26" s="12">
-        <f t="shared" ref="Q26" si="64">Q11/Q6</f>
+        <f t="shared" ref="Q26" si="65">Q11/Q6</f>
         <v>0.23224247952801458</v>
       </c>
       <c r="R26" s="12"/>
       <c r="S26" s="9"/>
       <c r="T26" s="12" t="e">
-        <f t="shared" ref="T26:X26" si="65">T11/T6</f>
+        <f t="shared" ref="T26:X26" si="66">T11/T6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U26" s="12" t="e">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V26" s="12" t="e">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W26" s="12">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.19469165329368746</v>
       </c>
       <c r="X26" s="12">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.20209794207341325</v>
       </c>
       <c r="Y26" s="12">
@@ -3065,11 +3065,11 @@
         <v>0.20448176443824698</v>
       </c>
       <c r="Z26" s="12">
-        <f t="shared" ref="Z26:AA26" si="66">Z11/Z6</f>
+        <f t="shared" ref="Z26:AA26" si="67">Z11/Z6</f>
         <v>0.21555861103107712</v>
       </c>
       <c r="AA26" s="12">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.22820935146106247</v>
       </c>
       <c r="AB26" s="9"/>
@@ -3088,19 +3088,19 @@
         <v>32</v>
       </c>
       <c r="C27" s="12">
-        <f t="shared" ref="C27:F27" si="67">C15/C6</f>
+        <f t="shared" ref="C27:F27" si="68">C15/C6</f>
         <v>0.16233393369995391</v>
       </c>
       <c r="D27" s="12">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.14910996488046577</v>
       </c>
       <c r="E27" s="12">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.1487804031623946</v>
       </c>
       <c r="F27" s="12">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.15153661394694881</v>
       </c>
       <c r="G27" s="12">
@@ -3108,65 +3108,65 @@
         <v>0.16440253935184193</v>
       </c>
       <c r="H27" s="12">
-        <f t="shared" ref="H27:J27" si="68">H15/H6</f>
+        <f t="shared" ref="H27:J27" si="69">H15/H6</f>
         <v>0.15751161987517118</v>
       </c>
       <c r="I27" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.1652034163794539</v>
       </c>
       <c r="J27" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.16777697511265993</v>
       </c>
       <c r="K27" s="12">
-        <f t="shared" ref="K27:L27" si="69">K15/K6</f>
+        <f t="shared" ref="K27:L27" si="70">K15/K6</f>
         <v>0.18069849259689941</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.17507142486307403</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" ref="M27:N27" si="70">M15/M6</f>
+        <f t="shared" ref="M27:N27" si="71">M15/M6</f>
         <v>0.1776422977672116</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.16803391146971208</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" ref="O27:P27" si="71">O15/O6</f>
+        <f t="shared" ref="O27:P27" si="72">O15/O6</f>
         <v>0.18069093293089852</v>
       </c>
       <c r="P27" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.17690871973919928</v>
       </c>
       <c r="Q27" s="12">
-        <f t="shared" ref="Q27" si="72">Q15/Q6</f>
+        <f t="shared" ref="Q27" si="73">Q15/Q6</f>
         <v>0.17684529415325442</v>
       </c>
       <c r="R27" s="12"/>
       <c r="S27" s="9"/>
       <c r="T27" s="12" t="e">
-        <f t="shared" ref="T27:X27" si="73">T15/T6</f>
+        <f t="shared" ref="T27:X27" si="74">T15/T6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U27" s="12" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V27" s="12" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W27" s="12">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.15611508162903961</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.15733190535465261</v>
       </c>
       <c r="Y27" s="12">
@@ -3174,11 +3174,11 @@
         <v>0.15290668346686492</v>
       </c>
       <c r="Z27" s="12">
-        <f t="shared" ref="Z27:AA27" si="74">Z15/Z6</f>
+        <f t="shared" ref="Z27:AA27" si="75">Z15/Z6</f>
         <v>0.16376524430749803</v>
       </c>
       <c r="AA27" s="12">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.17526588751202715</v>
       </c>
       <c r="AB27" s="9"/>
@@ -3197,19 +3197,19 @@
         <v>29</v>
       </c>
       <c r="C28" s="12">
-        <f t="shared" ref="C28:F28" si="75">C14/C13</f>
+        <f t="shared" ref="C28:F28" si="76">C14/C13</f>
         <v>0.14753426815818502</v>
       </c>
       <c r="D28" s="12">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.22111980555195285</v>
       </c>
       <c r="E28" s="12">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.22119149261651289</v>
       </c>
       <c r="F28" s="12">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.22358136582718244</v>
       </c>
       <c r="G28" s="12">
@@ -3217,65 +3217,65 @@
         <v>0.19173484679934685</v>
       </c>
       <c r="H28" s="12">
-        <f t="shared" ref="H28:J28" si="76">H14/H13</f>
+        <f t="shared" ref="H28:J28" si="77">H14/H13</f>
         <v>0.20982691163250072</v>
       </c>
       <c r="I28" s="12">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.19889560661023792</v>
       </c>
       <c r="J28" s="12">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.21355467912637824</v>
       </c>
       <c r="K28" s="12">
-        <f t="shared" ref="K28:L28" si="77">K14/K13</f>
+        <f t="shared" ref="K28:L28" si="78">K14/K13</f>
         <v>0.15769516008213744</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.20716756793067526</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" ref="M28:N28" si="78">M14/M13</f>
+        <f t="shared" ref="M28:N28" si="79">M14/M13</f>
         <v>0.20964023477332638</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.22098659228556763</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" ref="O28:P28" si="79">O14/O13</f>
+        <f t="shared" ref="O28:P28" si="80">O14/O13</f>
         <v>0.17581099064115718</v>
       </c>
       <c r="P28" s="12">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.21186977330295428</v>
       </c>
       <c r="Q28" s="12">
-        <f t="shared" ref="Q28" si="80">Q14/Q13</f>
+        <f t="shared" ref="Q28" si="81">Q14/Q13</f>
         <v>0.20553615274064546</v>
       </c>
       <c r="R28" s="12"/>
       <c r="S28" s="9"/>
       <c r="T28" s="12" t="e">
-        <f t="shared" ref="T28:X28" si="81">T14/T13</f>
+        <f t="shared" ref="T28:X28" si="82">T14/T13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U28" s="12" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V28" s="12" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W28" s="12">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.13727908156014879</v>
       </c>
       <c r="X28" s="12">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.17548479818090604</v>
       </c>
       <c r="Y28" s="12">
@@ -3283,11 +3283,11 @@
         <v>0.20385577634087509</v>
       </c>
       <c r="Z28" s="12">
-        <f t="shared" ref="Z28:AA28" si="82">Z14/Z13</f>
+        <f t="shared" ref="Z28:AA28" si="83">Z14/Z13</f>
         <v>0.20370686575785288</v>
       </c>
       <c r="AA28" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.19959394082330104</v>
       </c>
       <c r="AB28" s="9"/>

--- a/CTAS.xlsx
+++ b/CTAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3009995A-A1CF-44FA-AD6C-67B91992D3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43D0B0B-9DC9-4594-BC71-B1AF2847500D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{F251087B-52A6-4D65-A029-73EBA2C6E29C}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{F251087B-52A6-4D65-A029-73EBA2C6E29C}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,24 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={13379B2E-97F6-4993-AC1F-AF96FAD1D37D}</author>
+  </authors>
+  <commentList>
+    <comment ref="AA18" authorId="0" shapeId="0" xr:uid="{13379B2E-97F6-4993-AC1F-AF96FAD1D37D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    1 for 4 stock split Sept. 12 2024</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -231,7 +249,7 @@
     <t>IR</t>
   </si>
   <si>
-    <t>FQ326</t>
+    <t>FQ426</t>
   </si>
 </sst>
 </file>
@@ -242,7 +260,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +322,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -367,6 +391,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Oscar Settje" id="{B9A88E5B-6800-4318-986D-2810CF6D060A}" userId="7ff36870b9739543" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -684,6 +714,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="AA18" dT="2026-08-12T09:17:09.84" personId="{B9A88E5B-6800-4318-986D-2810CF6D060A}" id="{13379B2E-97F6-4993-AC1F-AF96FAD1D37D}">
+    <text>1 for 4 stock split Sept. 12 2024</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1B1AAB-DE15-4BFB-9872-3F4DEA47ED33}">
   <dimension ref="A1:L13"/>
@@ -709,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2">
-        <v>202.53</v>
+        <v>205.28</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -717,7 +755,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="9">
-        <v>400.4</v>
+        <v>400.16956099999999</v>
       </c>
       <c r="L3" s="14" t="s">
         <v>64</v>
@@ -732,7 +770,7 @@
       </c>
       <c r="K4" s="3">
         <f>K3*K2</f>
-        <v>81093.012000000002</v>
+        <v>82146.807482079996</v>
       </c>
       <c r="L4" s="4"/>
     </row>
@@ -744,7 +782,7 @@
         <v>4</v>
       </c>
       <c r="K5" s="3">
-        <v>183.20400000000001</v>
+        <v>289.01799999999997</v>
       </c>
       <c r="L5" s="14" t="s">
         <v>64</v>
@@ -755,8 +793,8 @@
         <v>5</v>
       </c>
       <c r="K6" s="3">
-        <f>229.49+2427.301</f>
-        <v>2656.7910000000002</v>
+        <f>998.987+1429.086</f>
+        <v>2428.0729999999999</v>
       </c>
       <c r="L6" s="14" t="s">
         <v>64</v>
@@ -768,7 +806,7 @@
       </c>
       <c r="K7" s="3">
         <f>K4-K5+K6</f>
-        <v>83566.599000000002</v>
+        <v>84285.862482080003</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -796,7 +834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC5E5BD-8069-4607-B39E-3C3E84BAF675}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC5E5BD-8069-4607-B39E-3C3E84BAF675}">
   <dimension ref="A1:AK175"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -965,7 +1003,9 @@
       <c r="AA3" s="9">
         <v>7976.0730000000003</v>
       </c>
-      <c r="AB3" s="9"/>
+      <c r="AB3" s="9">
+        <v>8621.6239999999998</v>
+      </c>
       <c r="AC3" s="9"/>
       <c r="AD3" s="9"/>
       <c r="AE3" s="9"/>
@@ -1045,7 +1085,9 @@
       <c r="AA4" s="9">
         <v>1218.0899999999999</v>
       </c>
-      <c r="AB4" s="9"/>
+      <c r="AB4" s="9">
+        <v>1391.8530000000001</v>
+      </c>
       <c r="AC4" s="9"/>
       <c r="AD4" s="9"/>
       <c r="AE4" s="9"/>
@@ -1128,7 +1170,9 @@
       <c r="AA5" s="9">
         <v>1146.018</v>
       </c>
-      <c r="AB5" s="9"/>
+      <c r="AB5" s="9">
+        <v>1251.2840000000001</v>
+      </c>
       <c r="AC5" s="9"/>
       <c r="AD5" s="9"/>
       <c r="AE5" s="9"/>
@@ -1235,7 +1279,10 @@
         <f>SUM(AA3:AA5)</f>
         <v>10340.181</v>
       </c>
-      <c r="AB6" s="9"/>
+      <c r="AB6" s="10">
+        <f>SUM(AB3:AB5)</f>
+        <v>11264.760999999999</v>
+      </c>
       <c r="AC6" s="9"/>
       <c r="AD6" s="9"/>
       <c r="AE6" s="9"/>
@@ -1318,7 +1365,9 @@
       <c r="AA7" s="9">
         <v>4040.8879999999999</v>
       </c>
-      <c r="AB7" s="9"/>
+      <c r="AB7" s="9">
+        <v>4312.0969999999998</v>
+      </c>
       <c r="AC7" s="9"/>
       <c r="AD7" s="9"/>
       <c r="AE7" s="9"/>
@@ -1401,7 +1450,9 @@
       <c r="AA8" s="9">
         <v>1125.1289999999999</v>
       </c>
-      <c r="AB8" s="9"/>
+      <c r="AB8" s="9">
+        <v>1244.8710000000001</v>
+      </c>
       <c r="AC8" s="9"/>
       <c r="AD8" s="9"/>
       <c r="AE8" s="9"/>
@@ -1511,7 +1562,10 @@
         <f>AA6-SUM(AA7:AA8)</f>
         <v>5174.1640000000007</v>
       </c>
-      <c r="AB9" s="9"/>
+      <c r="AB9" s="9">
+        <f>AB6-SUM(AB7:AB8)</f>
+        <v>5707.7929999999988</v>
+      </c>
       <c r="AC9" s="9"/>
       <c r="AD9" s="9"/>
       <c r="AE9" s="9"/>
@@ -1594,7 +1648,10 @@
       <c r="AA10" s="9">
         <v>2814.4380000000001</v>
       </c>
-      <c r="AB10" s="9"/>
+      <c r="AB10" s="9">
+        <f>3086.145+15.136</f>
+        <v>3101.2809999999999</v>
+      </c>
       <c r="AC10" s="9"/>
       <c r="AD10" s="9"/>
       <c r="AE10" s="9"/>
@@ -1703,7 +1760,10 @@
         <f>AA9-AA10</f>
         <v>2359.7260000000006</v>
       </c>
-      <c r="AB11" s="9"/>
+      <c r="AB11" s="9">
+        <f>AB9-AB10</f>
+        <v>2606.5119999999988</v>
+      </c>
       <c r="AC11" s="9"/>
       <c r="AD11" s="9"/>
       <c r="AE11" s="9"/>
@@ -1803,7 +1863,10 @@
         <f>-101.108+5.584</f>
         <v>-95.524000000000001</v>
       </c>
-      <c r="AB12" s="9"/>
+      <c r="AB12" s="9">
+        <f>-106.285+5.107</f>
+        <v>-101.178</v>
+      </c>
       <c r="AC12" s="9"/>
       <c r="AD12" s="9"/>
       <c r="AE12" s="9"/>
@@ -1839,7 +1902,7 @@
         <v>476.43399999999991</v>
       </c>
       <c r="H13" s="9">
-        <f t="shared" ref="H13:AA13" si="15">H11+H12</f>
+        <f t="shared" ref="H13:AB13" si="15">H11+H12</f>
         <v>473.86199999999974</v>
       </c>
       <c r="I13" s="9">
@@ -1912,7 +1975,10 @@
         <f t="shared" si="15"/>
         <v>2264.2020000000007</v>
       </c>
-      <c r="AB13" s="9"/>
+      <c r="AB13" s="9">
+        <f t="shared" si="15"/>
+        <v>2505.3339999999989</v>
+      </c>
       <c r="AC13" s="9"/>
       <c r="AD13" s="9"/>
       <c r="AE13" s="9"/>
@@ -1995,7 +2061,9 @@
       <c r="AA14" s="9">
         <v>451.92099999999999</v>
       </c>
-      <c r="AB14" s="9"/>
+      <c r="AB14" s="9">
+        <v>505.36599999999999</v>
+      </c>
       <c r="AC14" s="9"/>
       <c r="AD14" s="9"/>
       <c r="AE14" s="9"/>
@@ -2027,7 +2095,7 @@
         <v>346.18100000000015</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" ref="G15:AA15" si="20">G13-G14</f>
+        <f t="shared" ref="G15:AB15" si="20">G13-G14</f>
         <v>385.08499999999992</v>
       </c>
       <c r="H15" s="9">
@@ -2104,7 +2172,10 @@
         <f t="shared" si="20"/>
         <v>1812.2810000000006</v>
       </c>
-      <c r="AB15" s="9"/>
+      <c r="AB15" s="9">
+        <f t="shared" si="20"/>
+        <v>1999.9679999999989</v>
+      </c>
       <c r="AC15" s="9"/>
       <c r="AD15" s="9"/>
       <c r="AE15" s="9"/>
@@ -2228,9 +2299,13 @@
         <v>15.4</v>
       </c>
       <c r="AA17" s="9">
-        <v>15.4</v>
-      </c>
-      <c r="AB17" s="9"/>
+        <f>+AA15/AA18</f>
+        <v>4.4910688176839413</v>
+      </c>
+      <c r="AB17" s="9">
+        <f>+AB15/AB18</f>
+        <v>4.9841327594843312</v>
+      </c>
       <c r="AC17" s="9"/>
       <c r="AD17" s="9"/>
       <c r="AE17" s="9"/>
@@ -2316,8 +2391,12 @@
         <f>Z15/Z17</f>
         <v>102.05142857142857</v>
       </c>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
+      <c r="AA18" s="9">
+        <v>403.53</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>401.267</v>
+      </c>
       <c r="AC18" s="9"/>
       <c r="AD18" s="9"/>
       <c r="AE18" s="9"/>
@@ -2448,7 +2527,10 @@
         <f>+AA3/Z3-1</f>
         <v>6.8434076573176572E-2</v>
       </c>
-      <c r="AB20" s="9"/>
+      <c r="AB20" s="12">
+        <f>+AB3/AA3-1</f>
+        <v>8.0935944292385376E-2</v>
+      </c>
       <c r="AC20" s="9"/>
       <c r="AD20" s="9"/>
       <c r="AE20" s="9"/>
@@ -2542,7 +2624,10 @@
         <f>+(AA4+AA5)/(+SUM(Z4:Z5))-1</f>
         <v>0.10917249377878369</v>
       </c>
-      <c r="AB21" s="9"/>
+      <c r="AB21" s="12">
+        <f>+(AB4+AB5)/(+SUM(AA4:AA5))-1</f>
+        <v>0.11802717980735222</v>
+      </c>
       <c r="AC21" s="9"/>
       <c r="AD21" s="9"/>
       <c r="AE21" s="9"/>
@@ -2629,14 +2714,17 @@
         <v>0.12239035177343238</v>
       </c>
       <c r="Z22" s="13">
-        <f t="shared" ref="Z22:AA22" si="36">Z6/Y6-1</f>
+        <f t="shared" ref="Z22:AB22" si="36">Z6/Y6-1</f>
         <v>8.8573781822096187E-2</v>
       </c>
       <c r="AA22" s="13">
         <f t="shared" si="36"/>
         <v>7.7482112182264418E-2</v>
       </c>
-      <c r="AB22" s="10"/>
+      <c r="AB22" s="13">
+        <f t="shared" si="36"/>
+        <v>8.9416229754585297E-2</v>
+      </c>
       <c r="AC22" s="9"/>
       <c r="AD22" s="9"/>
       <c r="AE22" s="9"/>
@@ -2745,7 +2833,10 @@
         <f t="shared" si="43"/>
         <v>0.49337374419717578</v>
       </c>
-      <c r="AB23" s="9"/>
+      <c r="AB23" s="12">
+        <f t="shared" ref="AB23" si="44">(AB3-AB7)/AB3</f>
+        <v>0.49985095615396824</v>
+      </c>
       <c r="AC23" s="9"/>
       <c r="AD23" s="9"/>
       <c r="AE23" s="9"/>
@@ -2761,19 +2852,19 @@
         <v>34</v>
       </c>
       <c r="C24" s="12">
-        <f t="shared" ref="C24:F24" si="44">(C5-C8)/C5</f>
+        <f t="shared" ref="C24:F24" si="45">(C5-C8)/C5</f>
         <v>0.47176123683008953</v>
       </c>
       <c r="D24" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.47150069589197863</v>
       </c>
       <c r="E24" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.47667579106877916</v>
       </c>
       <c r="F24" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.473846244119977</v>
       </c>
       <c r="G24" s="12">
@@ -2781,65 +2872,65 @@
         <v>0.50887770244711494</v>
       </c>
       <c r="H24" s="12">
-        <f t="shared" ref="H24:J24" si="45">(H5-H8)/H5</f>
+        <f t="shared" ref="H24:J24" si="46">(H5-H8)/H5</f>
         <v>0.5036448394049009</v>
       </c>
       <c r="I24" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.51255545001142511</v>
       </c>
       <c r="J24" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.51328372741158967</v>
       </c>
       <c r="K24" s="12">
-        <f t="shared" ref="K24:L24" si="46">(K5-K8)/K5</f>
+        <f t="shared" ref="K24:L24" si="47">(K5-K8)/K5</f>
         <v>0.52744351367155851</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.52565486993610133</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" ref="M24:N24" si="47">(M5-M8)/M5</f>
+        <f t="shared" ref="M24:N24" si="48">(M5-M8)/M5</f>
         <v>0.52355297058748496</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.52015159222069451</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" ref="O24:P24" si="48">(O5-O8)/O5</f>
+        <f t="shared" ref="O24:P24" si="49">(O5-O8)/O5</f>
         <v>0.52315582659284021</v>
       </c>
       <c r="P24" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.52483276242956789</v>
       </c>
       <c r="Q24" s="12">
-        <f t="shared" ref="Q24" si="49">(Q5-Q8)/Q5</f>
+        <f t="shared" ref="Q24" si="50">(Q5-Q8)/Q5</f>
         <v>0.53317288939157303</v>
       </c>
       <c r="R24" s="12"/>
       <c r="S24" s="9"/>
       <c r="T24" s="12" t="e">
-        <f t="shared" ref="T24:X24" si="50">(T4+T5-T8)/(T4+T5)</f>
+        <f t="shared" ref="T24:X24" si="51">(T4+T5-T8)/(T4+T5)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U24" s="12" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V24" s="12" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W24" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.42652946503419065</v>
       </c>
       <c r="X24" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.44344596765918326</v>
       </c>
       <c r="Y24" s="12">
@@ -2847,14 +2938,17 @@
         <v>0.47346739016563305</v>
       </c>
       <c r="Z24" s="12">
-        <f t="shared" ref="Z24:AA24" si="51">(Z4+Z5-Z8)/(Z4+Z5)</f>
+        <f t="shared" ref="Z24:AA24" si="52">(Z4+Z5-Z8)/(Z4+Z5)</f>
         <v>0.50965555292819431</v>
       </c>
       <c r="AA24" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.52407884918963099</v>
       </c>
-      <c r="AB24" s="9"/>
+      <c r="AB24" s="12">
+        <f t="shared" ref="AB24" si="53">(AB4+AB5-AB8)/(AB4+AB5)</f>
+        <v>0.52901760294680145</v>
+      </c>
       <c r="AC24" s="9"/>
       <c r="AD24" s="9"/>
       <c r="AE24" s="9"/>
@@ -2870,19 +2964,19 @@
         <v>30</v>
       </c>
       <c r="C25" s="12">
-        <f t="shared" ref="C25:F25" si="52">C9/C6</f>
+        <f t="shared" ref="C25:F25" si="54">C9/C6</f>
         <v>0.47455981063987512</v>
       </c>
       <c r="D25" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.47012126768736168</v>
       </c>
       <c r="E25" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.47216329236807908</v>
       </c>
       <c r="F25" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.47659961540330342</v>
       </c>
       <c r="G25" s="12">
@@ -2890,65 +2984,65 @@
         <v>0.48736557188782109</v>
       </c>
       <c r="H25" s="12">
-        <f t="shared" ref="H25:J25" si="53">H9/H6</f>
+        <f t="shared" ref="H25:J25" si="55">H9/H6</f>
         <v>0.4802116123452313</v>
       </c>
       <c r="I25" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.49366691422437198</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.49189841092541897</v>
       </c>
       <c r="K25" s="12">
-        <f t="shared" ref="K25:L25" si="54">K9/K6</f>
+        <f t="shared" ref="K25:L25" si="56">K9/K6</f>
         <v>0.50053466059745266</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0.49836500593531935</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" ref="M25:N25" si="55">M9/M6</f>
+        <f t="shared" ref="M25:N25" si="57">M9/M6</f>
         <v>0.50565757012125367</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0.49706221051321553</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" ref="O25:P25" si="56">O9/O6</f>
+        <f t="shared" ref="O25:P25" si="58">O9/O6</f>
         <v>0.5027592580465482</v>
       </c>
       <c r="P25" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0.50446036988677112</v>
       </c>
       <c r="Q25" s="12">
-        <f t="shared" ref="Q25" si="57">Q9/Q6</f>
+        <f t="shared" ref="Q25" si="59">Q9/Q6</f>
         <v>0.50976053020928791</v>
       </c>
       <c r="R25" s="12"/>
       <c r="S25" s="9"/>
       <c r="T25" s="12" t="e">
-        <f t="shared" ref="T25:X25" si="58">T9/T6</f>
+        <f t="shared" ref="T25:X25" si="60">T9/T6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U25" s="12" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V25" s="12" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W25" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0.46578030279610022</v>
       </c>
       <c r="X25" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>0.46244381694525361</v>
       </c>
       <c r="Y25" s="12">
@@ -2956,14 +3050,17 @@
         <v>0.47339806657819644</v>
       </c>
       <c r="Z25" s="12">
-        <f t="shared" ref="Z25:AA25" si="59">Z9/Z6</f>
+        <f t="shared" ref="Z25:AA25" si="61">Z9/Z6</f>
         <v>0.48834052423693147</v>
       </c>
       <c r="AA25" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.50039394861656683</v>
       </c>
-      <c r="AB25" s="9"/>
+      <c r="AB25" s="12">
+        <f t="shared" ref="AB25" si="62">AB9/AB6</f>
+        <v>0.50669454948933224</v>
+      </c>
       <c r="AC25" s="9"/>
       <c r="AD25" s="9"/>
       <c r="AE25" s="9"/>
@@ -2979,19 +3076,19 @@
         <v>31</v>
       </c>
       <c r="C26" s="12">
-        <f t="shared" ref="C26:F26" si="60">C11/C6</f>
+        <f t="shared" ref="C26:F26" si="63">C11/C6</f>
         <v>0.20315224786679059</v>
       </c>
       <c r="D26" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.2045807128557359</v>
       </c>
       <c r="E26" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.20402504856195425</v>
       </c>
       <c r="F26" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.20608622302493668</v>
       </c>
       <c r="G26" s="12">
@@ -2999,65 +3096,65 @@
         <v>0.21370003372710078</v>
       </c>
       <c r="H26" s="12">
-        <f t="shared" ref="H26:J26" si="61">H11/H6</f>
+        <f t="shared" ref="H26:J26" si="64">H11/H6</f>
         <v>0.21020016599521191</v>
       </c>
       <c r="I26" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>0.21644328982163782</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>0.22161408535635307</v>
       </c>
       <c r="K26" s="12">
-        <f t="shared" ref="K26:L26" si="62">K11/K6</f>
+        <f t="shared" ref="K26:L26" si="65">K11/K6</f>
         <v>0.22427003338280851</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>0.23085093468104065</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" ref="M26:N26" si="63">M11/M6</f>
+        <f t="shared" ref="M26:N26" si="66">M11/M6</f>
         <v>0.23373546801862211</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>0.22396174613480332</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" ref="O26:P26" si="64">O11/O6</f>
+        <f t="shared" ref="O26:P26" si="67">O11/O6</f>
         <v>0.22731098898430599</v>
       </c>
       <c r="P26" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>0.23418424052640155</v>
       </c>
       <c r="Q26" s="12">
-        <f t="shared" ref="Q26" si="65">Q11/Q6</f>
+        <f t="shared" ref="Q26" si="68">Q11/Q6</f>
         <v>0.23224247952801458</v>
       </c>
       <c r="R26" s="12"/>
       <c r="S26" s="9"/>
       <c r="T26" s="12" t="e">
-        <f t="shared" ref="T26:X26" si="66">T11/T6</f>
+        <f t="shared" ref="T26:X26" si="69">T11/T6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U26" s="12" t="e">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V26" s="12" t="e">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W26" s="12">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>0.19469165329368746</v>
       </c>
       <c r="X26" s="12">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>0.20209794207341325</v>
       </c>
       <c r="Y26" s="12">
@@ -3065,14 +3162,17 @@
         <v>0.20448176443824698</v>
       </c>
       <c r="Z26" s="12">
-        <f t="shared" ref="Z26:AA26" si="67">Z11/Z6</f>
+        <f t="shared" ref="Z26:AA26" si="70">Z11/Z6</f>
         <v>0.21555861103107712</v>
       </c>
       <c r="AA26" s="12">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>0.22820935146106247</v>
       </c>
-      <c r="AB26" s="9"/>
+      <c r="AB26" s="12">
+        <f t="shared" ref="AB26" si="71">AB11/AB6</f>
+        <v>0.23138635608869101</v>
+      </c>
       <c r="AC26" s="9"/>
       <c r="AD26" s="9"/>
       <c r="AE26" s="9"/>
@@ -3088,19 +3188,19 @@
         <v>32</v>
       </c>
       <c r="C27" s="12">
-        <f t="shared" ref="C27:F27" si="68">C15/C6</f>
+        <f t="shared" ref="C27:F27" si="72">C15/C6</f>
         <v>0.16233393369995391</v>
       </c>
       <c r="D27" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>0.14910996488046577</v>
       </c>
       <c r="E27" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>0.1487804031623946</v>
       </c>
       <c r="F27" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>0.15153661394694881</v>
       </c>
       <c r="G27" s="12">
@@ -3108,65 +3208,65 @@
         <v>0.16440253935184193</v>
       </c>
       <c r="H27" s="12">
-        <f t="shared" ref="H27:J27" si="69">H15/H6</f>
+        <f t="shared" ref="H27:J27" si="73">H15/H6</f>
         <v>0.15751161987517118</v>
       </c>
       <c r="I27" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.1652034163794539</v>
       </c>
       <c r="J27" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.16777697511265993</v>
       </c>
       <c r="K27" s="12">
-        <f t="shared" ref="K27:L27" si="70">K15/K6</f>
+        <f t="shared" ref="K27:L27" si="74">K15/K6</f>
         <v>0.18069849259689941</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.17507142486307403</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" ref="M27:N27" si="71">M15/M6</f>
+        <f t="shared" ref="M27:N27" si="75">M15/M6</f>
         <v>0.1776422977672116</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0.16803391146971208</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" ref="O27:P27" si="72">O15/O6</f>
+        <f t="shared" ref="O27:P27" si="76">O15/O6</f>
         <v>0.18069093293089852</v>
       </c>
       <c r="P27" s="12">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>0.17690871973919928</v>
       </c>
       <c r="Q27" s="12">
-        <f t="shared" ref="Q27" si="73">Q15/Q6</f>
+        <f t="shared" ref="Q27" si="77">Q15/Q6</f>
         <v>0.17684529415325442</v>
       </c>
       <c r="R27" s="12"/>
       <c r="S27" s="9"/>
       <c r="T27" s="12" t="e">
-        <f t="shared" ref="T27:X27" si="74">T15/T6</f>
+        <f t="shared" ref="T27:X27" si="78">T15/T6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U27" s="12" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V27" s="12" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W27" s="12">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.15611508162903961</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.15733190535465261</v>
       </c>
       <c r="Y27" s="12">
@@ -3174,14 +3274,17 @@
         <v>0.15290668346686492</v>
       </c>
       <c r="Z27" s="12">
-        <f t="shared" ref="Z27:AA27" si="75">Z15/Z6</f>
+        <f t="shared" ref="Z27:AA27" si="79">Z15/Z6</f>
         <v>0.16376524430749803</v>
       </c>
       <c r="AA27" s="12">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0.17526588751202715</v>
       </c>
-      <c r="AB27" s="9"/>
+      <c r="AB27" s="12">
+        <f t="shared" ref="AB27" si="80">AB15/AB6</f>
+        <v>0.17754198247082198</v>
+      </c>
       <c r="AC27" s="9"/>
       <c r="AD27" s="9"/>
       <c r="AE27" s="9"/>
@@ -3197,19 +3300,19 @@
         <v>29</v>
       </c>
       <c r="C28" s="12">
-        <f t="shared" ref="C28:F28" si="76">C14/C13</f>
+        <f t="shared" ref="C28:F28" si="81">C14/C13</f>
         <v>0.14753426815818502</v>
       </c>
       <c r="D28" s="12">
-        <f t="shared" si="76"/>
+        <f t="shared" si="81"/>
         <v>0.22111980555195285</v>
       </c>
       <c r="E28" s="12">
-        <f t="shared" si="76"/>
+        <f t="shared" si="81"/>
         <v>0.22119149261651289</v>
       </c>
       <c r="F28" s="12">
-        <f t="shared" si="76"/>
+        <f t="shared" si="81"/>
         <v>0.22358136582718244</v>
       </c>
       <c r="G28" s="12">
@@ -3217,65 +3320,65 @@
         <v>0.19173484679934685</v>
       </c>
       <c r="H28" s="12">
-        <f t="shared" ref="H28:J28" si="77">H14/H13</f>
+        <f t="shared" ref="H28:J28" si="82">H14/H13</f>
         <v>0.20982691163250072</v>
       </c>
       <c r="I28" s="12">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.19889560661023792</v>
       </c>
       <c r="J28" s="12">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.21355467912637824</v>
       </c>
       <c r="K28" s="12">
-        <f t="shared" ref="K28:L28" si="78">K14/K13</f>
+        <f t="shared" ref="K28:L28" si="83">K14/K13</f>
         <v>0.15769516008213744</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="83"/>
         <v>0.20716756793067526</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" ref="M28:N28" si="79">M14/M13</f>
+        <f t="shared" ref="M28:N28" si="84">M14/M13</f>
         <v>0.20964023477332638</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>0.22098659228556763</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" ref="O28:P28" si="80">O14/O13</f>
+        <f t="shared" ref="O28:P28" si="85">O14/O13</f>
         <v>0.17581099064115718</v>
       </c>
       <c r="P28" s="12">
-        <f t="shared" si="80"/>
+        <f t="shared" si="85"/>
         <v>0.21186977330295428</v>
       </c>
       <c r="Q28" s="12">
-        <f t="shared" ref="Q28" si="81">Q14/Q13</f>
+        <f t="shared" ref="Q28" si="86">Q14/Q13</f>
         <v>0.20553615274064546</v>
       </c>
       <c r="R28" s="12"/>
       <c r="S28" s="9"/>
       <c r="T28" s="12" t="e">
-        <f t="shared" ref="T28:X28" si="82">T14/T13</f>
+        <f t="shared" ref="T28:X28" si="87">T14/T13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U28" s="12" t="e">
-        <f t="shared" si="82"/>
+        <f t="shared" si="87"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V28" s="12" t="e">
-        <f t="shared" si="82"/>
+        <f t="shared" si="87"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W28" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="87"/>
         <v>0.13727908156014879</v>
       </c>
       <c r="X28" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="87"/>
         <v>0.17548479818090604</v>
       </c>
       <c r="Y28" s="12">
@@ -3283,14 +3386,17 @@
         <v>0.20385577634087509</v>
       </c>
       <c r="Z28" s="12">
-        <f t="shared" ref="Z28:AA28" si="83">Z14/Z13</f>
+        <f t="shared" ref="Z28:AA28" si="88">Z14/Z13</f>
         <v>0.20370686575785288</v>
       </c>
       <c r="AA28" s="12">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>0.19959394082330104</v>
       </c>
-      <c r="AB28" s="9"/>
+      <c r="AB28" s="12">
+        <f t="shared" ref="AB28" si="89">AB14/AB13</f>
+        <v>0.20171601870249645</v>
+      </c>
       <c r="AC28" s="9"/>
       <c r="AD28" s="9"/>
       <c r="AE28" s="9"/>
@@ -8745,5 +8851,6 @@
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{8F8011A0-B3A2-42B7-96FC-84F880CC64FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>